--- a/SSC/digital_io.xlsx
+++ b/SSC/digital_io.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$129</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="116">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -295,6 +295,150 @@
     </r>
   </si>
   <si>
+    <t>//0x2nnx</t>
+  </si>
+  <si>
+    <t>Manufacturer Specific Area (0x2000- 0x5FFF)</t>
+  </si>
+  <si>
+    <t>0x2000</t>
+  </si>
+  <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t>Motor_Config_SDO_RW</t>
+  </si>
+  <si>
+    <t>ro</t>
+  </si>
+  <si>
+    <t>UINT</t>
+  </si>
+  <si>
+    <t>Station_Address</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Comm_Address_High</t>
+  </si>
+  <si>
+    <t>CAN_Comm_Freq</t>
+  </si>
+  <si>
+    <t>CAN_Heartbeat_Time</t>
+  </si>
+  <si>
+    <t>Work_Mode</t>
+  </si>
+  <si>
+    <t>Modbus_Baudrate</t>
+  </si>
+  <si>
+    <t>Motor_Pole_Pairs</t>
+  </si>
+  <si>
+    <t>Start_Torque</t>
+  </si>
+  <si>
+    <t>Sensorless_Start_Spd</t>
+  </si>
+  <si>
+    <t>Deceleration_Time</t>
+  </si>
+  <si>
+    <t>Acceleration_Time</t>
+  </si>
+  <si>
+    <t>Current_Protect</t>
+  </si>
+  <si>
+    <t>Brake_Torque</t>
+  </si>
+  <si>
+    <t>Brake_Lock_Torque</t>
+  </si>
+  <si>
+    <t>High_Voltage_Alarm</t>
+  </si>
+  <si>
+    <t>Low_Voltage_Alarm</t>
+  </si>
+  <si>
+    <t>Speed_Loop_P</t>
+  </si>
+  <si>
+    <t>Speed_Loop_I</t>
+  </si>
+  <si>
+    <t>Speed_Loop_D</t>
+  </si>
+  <si>
+    <t>Over_Limit_Ratio_C</t>
+  </si>
+  <si>
+    <t>PWM_Output_Min</t>
+  </si>
+  <si>
+    <t>PWM_Output_Max</t>
+  </si>
+  <si>
+    <t>Current_Loop_P</t>
+  </si>
+  <si>
+    <t>Current_Loop_I</t>
+  </si>
+  <si>
+    <t>Current_Loop_D</t>
+  </si>
+  <si>
+    <t>Current_Loop_C</t>
+  </si>
+  <si>
+    <t>Temp_Alarm_Point</t>
+  </si>
+  <si>
+    <t>UDINT</t>
+  </si>
+  <si>
+    <t>Software_Speed_Max</t>
+  </si>
+  <si>
+    <t>Software_Speed_Min</t>
+  </si>
+  <si>
+    <t>0x2001</t>
+  </si>
+  <si>
+    <t>Motor_Config_SDO_RO</t>
+  </si>
+  <si>
+    <t>Ext_Motor_Speed_Set</t>
+  </si>
+  <si>
+    <t>Motor_Work_Status</t>
+  </si>
+  <si>
+    <t>Motor_Target_Speed</t>
+  </si>
+  <si>
+    <t>Given_Speed</t>
+  </si>
+  <si>
+    <t>Motor_State</t>
+  </si>
+  <si>
+    <t>Actual_Temp</t>
+  </si>
+  <si>
+    <t>Port_Speed_Voltage</t>
+  </si>
+  <si>
+    <t>Section_Speed_Port</t>
+  </si>
+  <si>
     <t>//0x6nnx</t>
   </si>
   <si>
@@ -304,28 +448,22 @@
     <t>0x6000</t>
   </si>
   <si>
-    <t>RECORD</t>
-  </si>
-  <si>
-    <t>NumOfEntries</t>
-  </si>
-  <si>
-    <t>ro</t>
-  </si>
-  <si>
-    <t>UDINT</t>
-  </si>
-  <si>
-    <t>InputCounter</t>
+    <t>Motor_TxPDO_Status</t>
+  </si>
+  <si>
+    <t>Motor_Alarm_Code</t>
   </si>
   <si>
     <t>tx</t>
   </si>
   <si>
-    <t>USINT</t>
-  </si>
-  <si>
-    <t>MY_VAL_8BIT_INPUT</t>
+    <t>Motor_Actual_Speed</t>
+  </si>
+  <si>
+    <t>Actual_Current</t>
+  </si>
+  <si>
+    <t>Bus_Voltage</t>
   </si>
   <si>
     <t>//0x7nnx</t>
@@ -337,16 +475,16 @@
     <t>0x7000</t>
   </si>
   <si>
-    <t>OutputCounter</t>
-  </si>
-  <si>
-    <t>rw</t>
+    <t>Motor_RxPDO_Control</t>
+  </si>
+  <si>
+    <t>Control_Command</t>
   </si>
   <si>
     <t>rx</t>
   </si>
   <si>
-    <t>MY_VAL_8BIT_OUTPUT</t>
+    <t>Target_Speed_RPM</t>
   </si>
   <si>
     <t>//0x8nnx</t>
@@ -359,9 +497,6 @@
   </si>
   <si>
     <t>Modbus Config</t>
-  </si>
-  <si>
-    <t>UINT</t>
   </si>
   <si>
     <t>Station_ID</t>
@@ -1423,7 +1558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:T60"/>
+  <dimension ref="B1:T131"/>
   <sheetFormatPr defaultColWidth="10.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.81666666666667" style="2" customWidth="1"/>
@@ -1978,7 +2113,7 @@
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
     </row>
-    <row r="30" ht="18" customHeight="1" outlineLevel="1" spans="2:16">
+    <row r="30" ht="13" customHeight="1" outlineLevel="1" spans="2:16">
       <c r="D30" s="14"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -1989,7 +2124,7 @@
       <c r="O30"/>
       <c r="P30"/>
     </row>
-    <row r="31" ht="14" customHeight="1" outlineLevel="1" spans="2:16">
+    <row r="31" ht="9" customHeight="1" outlineLevel="1" spans="2:16">
       <c r="D31" s="14"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -2021,7 +2156,7 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
-    <row r="33" ht="23" customHeight="1" outlineLevel="1" spans="2:16">
+    <row r="33" ht="12" customHeight="1" outlineLevel="1" spans="2:16">
       <c r="D33" s="14"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2032,7 +2167,7 @@
       <c r="O33"/>
       <c r="P33"/>
     </row>
-    <row r="34" ht="30" customHeight="1" outlineLevel="1" spans="2:16">
+    <row r="34" ht="15" customHeight="1" outlineLevel="1" spans="2:16">
       <c r="D34" s="14"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2073,7 +2208,7 @@
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="1" t="s">
+      <c r="F36" t="s">
         <v>43</v>
       </c>
       <c r="G36" s="1"/>
@@ -2093,21 +2228,18 @@
       <c r="D37" s="14">
         <v>1</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="1" t="s">
+      <c r="E37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" t="s">
         <v>46</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>4</v>
+      <c r="G37" s="1">
+        <v>1</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="L37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="N37"/>
@@ -2121,65 +2253,119 @@
       <c r="D38" s="14">
         <v>2</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" t="s">
         <v>48</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>4</v>
+      <c r="G38" s="1">
+        <v>0</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="L38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M38" s="2" t="s">
         <v>47</v>
       </c>
       <c r="N38"/>
       <c r="O38"/>
       <c r="P38"/>
     </row>
-    <row r="41" s="1" customFormat="1" spans="2:16">
-      <c r="B41" s="11" t="s">
+    <row r="39" spans="2:16">
+      <c r="B39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="14">
+        <v>3</v>
+      </c>
+      <c r="E39" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="L39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+    </row>
+    <row r="40" spans="2:16">
+      <c r="B40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="14">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="L40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+    </row>
+    <row r="41" spans="2:16">
+      <c r="B41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="14">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
+      <c r="G41" s="1">
+        <v>4</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="L41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
     </row>
     <row r="42" spans="2:16">
       <c r="B42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="14">
+        <v>6</v>
+      </c>
+      <c r="E42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="L42" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N42"/>
       <c r="O42"/>
@@ -2187,27 +2373,24 @@
     </row>
     <row r="43" spans="2:16">
       <c r="B43" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D43" s="14">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" t="s">
         <v>53</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="1">
         <v>4</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="L43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N43"/>
       <c r="O43"/>
@@ -2215,70 +2398,199 @@
     </row>
     <row r="44" spans="2:16">
       <c r="B44" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D44" s="14">
-        <v>2</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="1">
+        <v>192</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="L44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N44"/>
       <c r="O44"/>
       <c r="P44"/>
     </row>
-    <row r="50" s="1" customFormat="1" spans="2:16">
-      <c r="B50" s="11" t="s">
+    <row r="45" spans="2:16">
+      <c r="B45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="14">
+        <v>9</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2048</v>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="L45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+    </row>
+    <row r="46" spans="2:16">
+      <c r="B46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="14">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" t="s">
+        <v>56</v>
+      </c>
+      <c r="G46" s="1">
+        <v>200</v>
+      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="L46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+    </row>
+    <row r="47" spans="2:16">
+      <c r="B47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="14">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="G47" s="1">
+        <v>200</v>
+      </c>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="L47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+    </row>
+    <row r="48" spans="2:16">
+      <c r="B48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="14">
+        <v>12</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" t="s">
         <v>58</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
+      <c r="G48" s="1">
+        <v>900</v>
+      </c>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="L48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="14">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" t="s">
+        <v>59</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2047</v>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="L49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N49"/>
+      <c r="O49"/>
+      <c r="P49"/>
+    </row>
+    <row r="50" spans="2:16">
+      <c r="B50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="14">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" t="s">
+        <v>60</v>
+      </c>
+      <c r="G50" s="1">
+        <v>224</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="L50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N50"/>
+      <c r="O50"/>
+      <c r="P50"/>
     </row>
     <row r="51" spans="2:16">
       <c r="B51" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="D51" s="14">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" s="1">
+        <v>600</v>
+      </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="L51" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N51"/>
       <c r="O51"/>
@@ -2286,193 +2598,1212 @@
     </row>
     <row r="52" spans="2:16">
       <c r="B52" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D52" s="14">
-        <v>1</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" t="s">
+        <v>45</v>
+      </c>
+      <c r="F52" t="s">
         <v>62</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>4</v>
+      <c r="G52" s="1">
+        <v>85</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="L52" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M52" s="2"/>
+        <v>47</v>
+      </c>
       <c r="N52"/>
       <c r="O52"/>
       <c r="P52"/>
     </row>
-    <row r="53" s="1" customFormat="1" spans="2:16">
+    <row r="53" spans="2:16">
       <c r="B53" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>41</v>
+      </c>
       <c r="D53" s="14">
-        <v>2</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" t="s">
+        <v>45</v>
+      </c>
+      <c r="F53" t="s">
         <v>63</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="1">
         <v>64</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
       <c r="L53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M53" s="2"/>
+        <v>47</v>
+      </c>
       <c r="N53"/>
       <c r="O53"/>
       <c r="P53"/>
     </row>
     <row r="54" spans="2:16">
-      <c r="D54" s="14"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="B54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="14">
+        <v>18</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" t="s">
+        <v>64</v>
+      </c>
+      <c r="G54" s="1">
+        <v>32</v>
+      </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
+      <c r="L54" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N54"/>
       <c r="O54"/>
       <c r="P54"/>
     </row>
     <row r="55" spans="2:16">
-      <c r="D55" s="14"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
+      <c r="B55" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="14">
+        <v>19</v>
+      </c>
+      <c r="E55" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" t="s">
+        <v>65</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
+      <c r="L55" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N55"/>
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" s="1" customFormat="1" spans="2:16">
-      <c r="B56" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C56" s="11" t="s">
+    <row r="56" spans="2:16">
+      <c r="B56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" s="14">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>45</v>
+      </c>
+      <c r="F56" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
+      <c r="G56" s="1">
+        <v>80</v>
+      </c>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="L56" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
     </row>
     <row r="57" spans="2:16">
-      <c r="D57" s="14"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="B57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" s="14">
+        <v>21</v>
+      </c>
+      <c r="E57" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57" t="s">
+        <v>67</v>
+      </c>
+      <c r="G57" s="1">
+        <v>52</v>
+      </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
+      <c r="L57" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N57"/>
       <c r="O57"/>
       <c r="P57"/>
     </row>
     <row r="58" spans="2:16">
-      <c r="D58" s="14"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
+      <c r="B58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" s="14">
+        <v>22</v>
+      </c>
+      <c r="E58" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" t="s">
+        <v>68</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2047</v>
+      </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
+      <c r="L58" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N58"/>
       <c r="O58"/>
       <c r="P58"/>
     </row>
-    <row r="59" customFormat="1" spans="2:16">
-      <c r="B59" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15"/>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
-      <c r="N59" s="15"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="11"/>
+    <row r="59" spans="2:16">
+      <c r="B59" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59" s="14">
+        <v>23</v>
+      </c>
+      <c r="E59" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="L59" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
     </row>
     <row r="60" spans="2:16">
-      <c r="B60" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" t="s">
-        <v>42</v>
-      </c>
-      <c r="D60"/>
-      <c r="E60"/>
+      <c r="B60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="14">
+        <v>24</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F60" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60" t="s">
         <v>70</v>
       </c>
-      <c r="K60"/>
-      <c r="L60"/>
-      <c r="M60"/>
+      <c r="G60" s="1">
+        <v>32</v>
+      </c>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="L60" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="N60"/>
       <c r="O60"/>
       <c r="P60"/>
     </row>
+    <row r="61" spans="2:16">
+      <c r="B61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" s="14">
+        <v>25</v>
+      </c>
+      <c r="E61" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61" t="s">
+        <v>71</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="L61" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+    </row>
+    <row r="62" spans="2:16">
+      <c r="B62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26</v>
+      </c>
+      <c r="E62" t="s">
+        <v>45</v>
+      </c>
+      <c r="F62" t="s">
+        <v>72</v>
+      </c>
+      <c r="G62" s="1">
+        <v>32</v>
+      </c>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="L62" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="P62"/>
+    </row>
+    <row r="63" spans="2:16">
+      <c r="B63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" s="14">
+        <v>27</v>
+      </c>
+      <c r="E63" t="s">
+        <v>45</v>
+      </c>
+      <c r="F63" t="s">
+        <v>73</v>
+      </c>
+      <c r="G63" s="1">
+        <v>85</v>
+      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="L63" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N63"/>
+      <c r="O63"/>
+      <c r="P63"/>
+    </row>
+    <row r="64" spans="2:16">
+      <c r="B64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D64" s="14">
+        <v>28</v>
+      </c>
+      <c r="E64" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" t="s">
+        <v>75</v>
+      </c>
+      <c r="G64" s="1">
+        <v>37856</v>
+      </c>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="L64" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="P64"/>
+    </row>
+    <row r="65" spans="2:19">
+      <c r="B65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D65" s="14">
+        <v>29</v>
+      </c>
+      <c r="E65" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" t="s">
+        <v>76</v>
+      </c>
+      <c r="G65" s="1">
+        <v>20</v>
+      </c>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="L65" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+    </row>
+    <row r="67" spans="2:19">
+      <c r="B67" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D67" s="14"/>
+      <c r="E67"/>
+      <c r="F67" t="s">
+        <v>78</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="L67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="P67"/>
+    </row>
+    <row r="68" spans="2:19">
+      <c r="B68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D68" s="14">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>45</v>
+      </c>
+      <c r="F68" t="s">
+        <v>79</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="L68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N68"/>
+      <c r="O68"/>
+      <c r="P68"/>
+    </row>
+    <row r="69" spans="2:19">
+      <c r="B69" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" s="14">
+        <v>2</v>
+      </c>
+      <c r="E69" t="s">
+        <v>45</v>
+      </c>
+      <c r="F69" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="L69" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N69"/>
+      <c r="O69"/>
+      <c r="P69"/>
+    </row>
+    <row r="70" spans="2:19">
+      <c r="B70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="14">
+        <v>3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>74</v>
+      </c>
+      <c r="F70" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="L70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N70"/>
+      <c r="O70"/>
+      <c r="P70"/>
+    </row>
+    <row r="71" spans="2:19">
+      <c r="B71" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="14">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" t="s">
+        <v>82</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="L71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+    </row>
+    <row r="72" spans="2:19">
+      <c r="B72" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="14">
+        <v>5</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F72" t="s">
+        <v>83</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="L72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+    </row>
+    <row r="73" spans="2:19">
+      <c r="B73" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="14">
+        <v>6</v>
+      </c>
+      <c r="E73" t="s">
+        <v>45</v>
+      </c>
+      <c r="F73" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="L73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N73"/>
+      <c r="O73"/>
+      <c r="P73"/>
+    </row>
+    <row r="74" spans="2:19">
+      <c r="B74" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74" s="2">
+        <v>7</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q74"/>
+      <c r="R74"/>
+      <c r="S74"/>
+    </row>
+    <row r="75" spans="2:19">
+      <c r="B75" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D75" s="2">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="S75"/>
+    </row>
+    <row r="76" spans="2:19">
+      <c r="G76" s="14"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="Q76"/>
+      <c r="R76"/>
+      <c r="S76"/>
+    </row>
+    <row r="77" spans="2:19">
+      <c r="E77" s="14"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+    </row>
+    <row r="78" spans="2:19">
+      <c r="E78" s="14"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="O78"/>
+      <c r="P78"/>
+      <c r="Q78"/>
+    </row>
+    <row r="79" spans="2:19">
+      <c r="E79" s="14"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="O79"/>
+      <c r="P79"/>
+      <c r="Q79"/>
+    </row>
+    <row r="80" spans="2:19">
+      <c r="E80" s="14"/>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="O80"/>
+      <c r="P80"/>
+      <c r="Q80"/>
+    </row>
+    <row r="81" spans="2:17">
+      <c r="E81" s="14"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+    </row>
+    <row r="82" spans="2:17">
+      <c r="E82" s="14"/>
+      <c r="F82" s="1"/>
+      <c r="G82"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="O82"/>
+      <c r="P82"/>
+      <c r="Q82"/>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="2:17">
+      <c r="B83" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="11"/>
+      <c r="O83" s="11"/>
+      <c r="P83" s="11"/>
+    </row>
+    <row r="84" spans="2:17">
+      <c r="B84" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="14"/>
+      <c r="E84" s="1"/>
+      <c r="F84" t="s">
+        <v>90</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="L84" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N84"/>
+      <c r="O84"/>
+      <c r="P84"/>
+    </row>
+    <row r="85" spans="2:17">
+      <c r="B85" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D85" s="14">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" t="s">
+        <v>91</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="L85" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N85"/>
+      <c r="O85"/>
+      <c r="P85"/>
+    </row>
+    <row r="86" spans="2:17">
+      <c r="B86" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D86" s="14">
+        <v>2</v>
+      </c>
+      <c r="E86" t="s">
+        <v>74</v>
+      </c>
+      <c r="F86" t="s">
+        <v>93</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="L86" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N86"/>
+      <c r="O86"/>
+      <c r="P86"/>
+    </row>
+    <row r="87" spans="2:17">
+      <c r="B87" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="14">
+        <v>3</v>
+      </c>
+      <c r="E87" t="s">
+        <v>45</v>
+      </c>
+      <c r="F87" t="s">
+        <v>94</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="L87" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N87"/>
+      <c r="O87"/>
+      <c r="P87"/>
+    </row>
+    <row r="88" spans="2:17">
+      <c r="B88" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D88" s="14">
+        <v>4</v>
+      </c>
+      <c r="E88" t="s">
+        <v>45</v>
+      </c>
+      <c r="F88" t="s">
+        <v>95</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="L88" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N88"/>
+      <c r="O88"/>
+      <c r="P88"/>
+    </row>
+    <row r="89" spans="2:17">
+      <c r="B89" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="14">
+        <v>5</v>
+      </c>
+      <c r="E89" t="s">
+        <v>45</v>
+      </c>
+      <c r="F89" t="s">
+        <v>84</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="L89" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N89"/>
+      <c r="O89"/>
+      <c r="P89"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="2:17">
+      <c r="B91" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="11"/>
+      <c r="N91" s="11"/>
+      <c r="O91" s="11"/>
+      <c r="P91" s="11"/>
+    </row>
+    <row r="92" spans="2:17">
+      <c r="B92" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="14"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="L92" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N92"/>
+      <c r="O92"/>
+      <c r="P92"/>
+    </row>
+    <row r="93" spans="2:17">
+      <c r="B93" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D93" s="14">
+        <v>1</v>
+      </c>
+      <c r="E93" t="s">
+        <v>45</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="L93" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N93"/>
+      <c r="O93"/>
+      <c r="P93"/>
+    </row>
+    <row r="94" spans="2:17">
+      <c r="B94" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D94" s="14">
+        <v>2</v>
+      </c>
+      <c r="E94" t="s">
+        <v>45</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="L94" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N94"/>
+      <c r="O94"/>
+      <c r="P94"/>
+    </row>
+    <row r="95" spans="2:17">
+      <c r="D95" s="14"/>
+    </row>
+    <row r="96" spans="2:17">
+      <c r="D96" s="14"/>
+    </row>
+    <row r="97" spans="4:4">
+      <c r="D97" s="14"/>
+    </row>
+    <row r="98" spans="4:4">
+      <c r="D98" s="14"/>
+    </row>
+    <row r="99" spans="4:4">
+      <c r="D99" s="14"/>
+    </row>
+    <row r="100" spans="4:4">
+      <c r="D100" s="14"/>
+    </row>
+    <row r="101" spans="4:4">
+      <c r="D101" s="14"/>
+    </row>
+    <row r="102" spans="4:4">
+      <c r="D102" s="14"/>
+    </row>
+    <row r="103" spans="4:4">
+      <c r="D103" s="14"/>
+    </row>
+    <row r="104" spans="4:4">
+      <c r="D104" s="14"/>
+    </row>
+    <row r="105" spans="4:4">
+      <c r="D105" s="14"/>
+    </row>
+    <row r="106" spans="4:4">
+      <c r="D106" s="14"/>
+    </row>
+    <row r="107" spans="4:4">
+      <c r="D107" s="14"/>
+    </row>
+    <row r="108" spans="4:4">
+      <c r="D108" s="14"/>
+    </row>
+    <row r="121" s="1" customFormat="1" spans="2:16">
+      <c r="B121" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
+      <c r="F121" s="11"/>
+      <c r="G121" s="11"/>
+      <c r="H121" s="11"/>
+      <c r="I121" s="11"/>
+      <c r="J121" s="11"/>
+      <c r="K121" s="11"/>
+      <c r="L121" s="11"/>
+      <c r="M121" s="11"/>
+      <c r="N121" s="11"/>
+      <c r="O121" s="11"/>
+      <c r="P121" s="11"/>
+    </row>
+    <row r="122" spans="2:16">
+      <c r="B122" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D122" s="14"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="L122" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N122"/>
+      <c r="O122"/>
+      <c r="P122"/>
+    </row>
+    <row r="123" spans="2:16">
+      <c r="B123" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D123" s="14">
+        <v>1</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="L123" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N123"/>
+      <c r="O123"/>
+      <c r="P123"/>
+    </row>
+    <row r="124" s="1" customFormat="1" spans="2:16">
+      <c r="B124" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" s="14">
+        <v>2</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="2"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M124" s="2"/>
+      <c r="N124"/>
+      <c r="O124"/>
+      <c r="P124"/>
+    </row>
+    <row r="125" spans="2:16">
+      <c r="D125" s="14"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="N125"/>
+      <c r="O125"/>
+      <c r="P125"/>
+    </row>
+    <row r="126" spans="2:16">
+      <c r="D126" s="14"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="N126"/>
+      <c r="O126"/>
+      <c r="P126"/>
+    </row>
+    <row r="127" s="1" customFormat="1" spans="2:16">
+      <c r="B127" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="11"/>
+      <c r="J127" s="11"/>
+      <c r="K127" s="11"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="11"/>
+      <c r="O127" s="11"/>
+      <c r="P127" s="11"/>
+    </row>
+    <row r="128" spans="2:16">
+      <c r="D128" s="14"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="N128"/>
+      <c r="O128"/>
+      <c r="P128"/>
+    </row>
+    <row r="129" spans="2:16">
+      <c r="D129" s="14"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="N129"/>
+      <c r="O129"/>
+      <c r="P129"/>
+    </row>
+    <row r="130" customFormat="1" spans="2:16">
+      <c r="B130" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D130" s="15"/>
+      <c r="E130" s="15"/>
+      <c r="F130" s="15"/>
+      <c r="G130" s="15"/>
+      <c r="H130" s="15"/>
+      <c r="I130" s="15"/>
+      <c r="J130" s="15"/>
+      <c r="K130" s="15"/>
+      <c r="L130" s="15"/>
+      <c r="M130" s="15"/>
+      <c r="N130" s="15"/>
+      <c r="O130" s="11"/>
+      <c r="P130" s="11"/>
+    </row>
+    <row r="131" spans="2:16">
+      <c r="B131" t="s">
+        <v>114</v>
+      </c>
+      <c r="C131" t="s">
+        <v>42</v>
+      </c>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131" t="s">
+        <v>1</v>
+      </c>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+      <c r="J131" t="s">
+        <v>115</v>
+      </c>
+      <c r="K131"/>
+      <c r="L131"/>
+      <c r="M131"/>
+      <c r="N131"/>
+      <c r="O131"/>
+      <c r="P131"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B10:P53" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B10:P65" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C41 C50 C56"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C38 C42:C44 C51:C53 C54:C55 C57:C62">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C83 C91 C121 C127"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C90 C63:C66 C79:C82 C95:C100 C112:C120 C132:C902">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C63:C902">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:&#10;VARIABLE&#10;RECORD&#10;ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C24:C25 C27:C28 C30:C31 C33:C34 C36:C37 C61:C62 C84:C89 C92:C94 C122:C126 C128:C131">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J36:J38 J42:J44 J51:J53 J54:J55 J57:J62">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be &#10;M : (mandatory)&#10;O : (optional) &#10;C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J24:J25 J27:J28 J30:J31 J33:J34 J36:J37 J61:J62 J84:J89 J92:J94 J122:J126 J128:J131">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K36:K38 K42:K44 K51:K53 K54:K55 K57:K62">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be&#10;B : (Backup)&#10;S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K24:K25 K27:K28 K30:K31 K33:K34 K36:K37 K61:K62 K84:K89 K92:K94 K122:K126 K128:K131">
       <formula1>"B,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:M13 M15:M16 M18:M19 M21:M22 M24:M25 M27:M28 M30:M31 M33:M34 M36:M38 M42:M44 M51:M53 M54:M55 M57:M60">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12:M13 M15:M16 M18:M19 M21:M22 M24:M25 M27:M28 M30:M31 M33:M34 M36:M37 M84:M89 M92:M94 M122:M126 M128:M131">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
   </dataValidations>

--- a/SSC/digital_io.xlsx
+++ b/SSC/digital_io.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$124</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$187</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="157">
   <si>
     <t>Device Profile:</t>
   </si>
@@ -629,9 +629,6 @@
   </si>
   <si>
     <t>Modbus_Config_Slave2</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>//0xAnnx</t>
@@ -2125,8 +2122,6 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
       <c r="L21" s="2" t="s">
         <v>34</v>
       </c>
@@ -2141,7 +2136,6 @@
       <c r="B22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="2"/>
       <c r="D22" s="14">
         <v>1</v>
       </c>
@@ -2156,12 +2150,9 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
       <c r="L22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M22" s="2"/>
       <c r="N22"/>
       <c r="O22"/>
       <c r="P22"/>
@@ -2170,7 +2161,6 @@
       <c r="B23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="2"/>
       <c r="D23" s="14">
         <v>2</v>
       </c>
@@ -2185,12 +2175,9 @@
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
       <c r="L23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M23" s="2"/>
       <c r="N23"/>
       <c r="O23"/>
       <c r="P23"/>
@@ -2210,8 +2197,6 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
       <c r="L24" s="2" t="s">
         <v>34</v>
       </c>
@@ -2226,7 +2211,6 @@
       <c r="B25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="2"/>
       <c r="D25" s="14">
         <v>1</v>
       </c>
@@ -2241,12 +2225,9 @@
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M25" s="2"/>
       <c r="N25"/>
       <c r="O25"/>
       <c r="P25"/>
@@ -2255,7 +2236,6 @@
       <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="2"/>
       <c r="D26" s="14">
         <v>2</v>
       </c>
@@ -2270,12 +2250,9 @@
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
       <c r="L26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M26" s="2"/>
       <c r="N26"/>
       <c r="O26"/>
       <c r="P26"/>
@@ -2359,8 +2336,6 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
       <c r="L34" s="2" t="s">
         <v>34</v>
       </c>
@@ -2375,7 +2350,6 @@
       <c r="B35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="2"/>
       <c r="D35" s="14">
         <v>1</v>
       </c>
@@ -2390,12 +2364,9 @@
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
       <c r="L35" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M35" s="2"/>
       <c r="N35"/>
       <c r="O35"/>
       <c r="P35"/>
@@ -2404,7 +2375,6 @@
       <c r="B36" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="2"/>
       <c r="D36" s="14">
         <v>2</v>
       </c>
@@ -2419,12 +2389,9 @@
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
       <c r="L36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M36" s="2"/>
       <c r="N36"/>
       <c r="O36"/>
       <c r="P36"/>
@@ -2433,7 +2400,6 @@
       <c r="B37" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="2"/>
       <c r="D37" s="14">
         <v>3</v>
       </c>
@@ -2448,12 +2414,9 @@
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
       <c r="L37" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M37" s="2"/>
       <c r="N37"/>
       <c r="O37"/>
       <c r="P37"/>
@@ -2462,7 +2425,6 @@
       <c r="B38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="2"/>
       <c r="D38" s="14">
         <v>4</v>
       </c>
@@ -2477,12 +2439,9 @@
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
       <c r="L38" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M38" s="2"/>
       <c r="N38"/>
       <c r="O38"/>
       <c r="P38"/>
@@ -2491,7 +2450,6 @@
       <c r="B39" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="2"/>
       <c r="D39" s="14">
         <v>5</v>
       </c>
@@ -2506,12 +2464,9 @@
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
       <c r="L39" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M39" s="2"/>
       <c r="N39"/>
       <c r="O39"/>
       <c r="P39"/>
@@ -2531,8 +2486,6 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
       <c r="L40" s="2" t="s">
         <v>34</v>
       </c>
@@ -2547,7 +2500,6 @@
       <c r="B41" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="2"/>
       <c r="D41" s="14">
         <v>1</v>
       </c>
@@ -2562,12 +2514,9 @@
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
       <c r="L41" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M41" s="2"/>
       <c r="N41"/>
       <c r="O41"/>
       <c r="P41"/>
@@ -2576,7 +2525,6 @@
       <c r="B42" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="2"/>
       <c r="D42" s="14">
         <v>2</v>
       </c>
@@ -2591,12 +2539,9 @@
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
       <c r="L42" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M42" s="2"/>
       <c r="N42"/>
       <c r="O42"/>
       <c r="P42"/>
@@ -2605,7 +2550,6 @@
       <c r="B43" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="2"/>
       <c r="D43" s="14">
         <v>3</v>
       </c>
@@ -2620,12 +2564,9 @@
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
       <c r="L43" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M43" s="2"/>
       <c r="N43"/>
       <c r="O43"/>
       <c r="P43"/>
@@ -2634,7 +2575,6 @@
       <c r="B44" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="2"/>
       <c r="D44" s="14">
         <v>4</v>
       </c>
@@ -2649,12 +2589,9 @@
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
       <c r="L44" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M44" s="2"/>
       <c r="N44"/>
       <c r="O44"/>
       <c r="P44"/>
@@ -2663,7 +2600,6 @@
       <c r="B45" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="2"/>
       <c r="D45" s="14">
         <v>5</v>
       </c>
@@ -2678,12 +2614,9 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
       <c r="L45" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M45" s="2"/>
       <c r="N45"/>
       <c r="O45"/>
       <c r="P45"/>
@@ -2724,12 +2657,9 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
       <c r="L50" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M50" s="2"/>
       <c r="N50"/>
       <c r="O50"/>
       <c r="P50"/>
@@ -2738,7 +2668,6 @@
       <c r="B51" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="2"/>
       <c r="D51" s="14">
         <v>1</v>
       </c>
@@ -2753,12 +2682,9 @@
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
       <c r="L51" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M51" s="2"/>
       <c r="N51"/>
       <c r="O51"/>
       <c r="P51"/>
@@ -2767,7 +2693,6 @@
       <c r="B52" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="2"/>
       <c r="D52" s="14">
         <v>2</v>
       </c>
@@ -2782,12 +2707,9 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
       <c r="L52" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M52" s="2"/>
       <c r="N52"/>
       <c r="O52"/>
       <c r="P52"/>
@@ -2842,8 +2764,6 @@
       <c r="C57" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
       <c r="F57" s="14" t="s">
         <v>77</v>
       </c>
@@ -2855,16 +2775,12 @@
       <c r="L57" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
       <c r="P57"/>
     </row>
     <row r="58" spans="2:16">
       <c r="B58" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C58" s="2"/>
       <c r="D58" s="14">
         <v>1</v>
       </c>
@@ -2879,12 +2795,9 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
       <c r="L58" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M58" s="2"/>
       <c r="N58"/>
       <c r="O58"/>
       <c r="P58"/>
@@ -2893,7 +2806,6 @@
       <c r="B59" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="2"/>
       <c r="D59" s="14">
         <v>2</v>
       </c>
@@ -2908,12 +2820,9 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
       <c r="L59" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M59" s="2"/>
       <c r="N59"/>
       <c r="O59"/>
       <c r="P59"/>
@@ -5543,7 +5452,7 @@
         <v>144</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -5608,10 +5517,10 @@
     </row>
     <row r="185" s="1" customFormat="1" spans="2:16">
       <c r="B185" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C185" s="11" t="s">
         <v>152</v>
-      </c>
-      <c r="C185" s="11" t="s">
-        <v>153</v>
       </c>
       <c r="D185" s="11"/>
       <c r="E185" s="11"/>
@@ -5651,10 +5560,10 @@
     </row>
     <row r="188" customFormat="1" spans="2:16">
       <c r="B188" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C188" s="15" t="s">
         <v>154</v>
-      </c>
-      <c r="C188" s="15" t="s">
-        <v>155</v>
       </c>
       <c r="D188" s="15"/>
       <c r="E188" s="15"/>
@@ -5672,7 +5581,7 @@
     </row>
     <row r="189" spans="2:16">
       <c r="B189" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C189" t="s">
         <v>32</v>
@@ -5686,7 +5595,7 @@
       <c r="H189"/>
       <c r="I189"/>
       <c r="J189" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K189"/>
       <c r="L189"/>
@@ -5697,7 +5606,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B10:P95" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B10:P124" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
